--- a/cicada_generator/lib/WHO/schedule/WHO Vaccine Group.xlsx
+++ b/cicada_generator/lib/WHO/schedule/WHO Vaccine Group.xlsx
@@ -3,8 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="Vaccine Groups" sheetId="2" r:id="rId5"/>
+    <sheet state="visible" name="Vaccine Groups" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="Change History" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -12,9 +12,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="23">
-  <si>
-    <t xml:space="preserve">Vaccine Group Name</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="31">
+  <si>
+    <t xml:space="preserve">Vaccine Group</t>
   </si>
   <si>
     <t xml:space="preserve">Administer Full Vaccine Group</t>
@@ -81,6 +81,30 @@
   </si>
   <si>
     <t xml:space="preserve">COVID-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Version</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n/a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Publication Date: n/a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change #</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Previous Values</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reason for Change</t>
   </si>
 </sst>
 </file>
@@ -321,13 +345,171 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <sheetFormatPr defaultRowHeight="15.75" defaultColWidth="14.43"/>
-  <sheetData/>
-  <drawing r:id="rId1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -337,162 +519,33 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>24</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>3</v>
+        <v>27</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
